--- a/Task_manager_1-TC.xlsx
+++ b/Task_manager_1-TC.xlsx
@@ -1,447 +1,907 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="List 1" sheetId="1" r:id="rId5"/>
+    <sheet name="List 1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Funkce</t>
-  </si>
-  <si>
-    <t>Název</t>
-  </si>
-  <si>
-    <t>Popis</t>
-  </si>
-  <si>
-    <t>Vstupní podmínky</t>
-  </si>
-  <si>
-    <t>Kroky testu</t>
-  </si>
-  <si>
-    <t>Očekávaný výsledek</t>
-  </si>
-  <si>
-    <t>Skutečný výsledek</t>
-  </si>
-  <si>
-    <t>Poznámky</t>
-  </si>
-  <si>
-    <t>TC01</t>
-  </si>
-  <si>
-    <t>hlavni_menu()</t>
-  </si>
-  <si>
-    <t>Výběr volby 1 - přidání úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že volba 1 zobrazí výzvu k zadání úkolu a úkol je po vyplnění přidán do seznamu</t>
-  </si>
-  <si>
-    <t>Program zobrazuje hlavní menu, seznam úkolů je prázdný</t>
-  </si>
-  <si>
-    <t>1. Spusťte program. 
-2. Zadejte 1 a potvrďte Enterem. 
-3. Zadejte název "Úkol 1". 
-4. Zadejte popis "Popis pro úkol 1". 
-5. Zvolte 2 pro zobrazení seznamu.</t>
-  </si>
-  <si>
-    <t>Program zobrazí výzvu k zadání názvu a popisu. Po zadání zobrazí potvrzení Úkol 'Úkol 1' byl přidán. a úkol se objeví v seznamu.</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Základní navigace z menu</t>
-  </si>
-  <si>
-    <t>TC02</t>
-  </si>
-  <si>
-    <t>Výběr volby 2 - zobrazení úkolů</t>
-  </si>
-  <si>
-    <t>Ověření, že volba 2 zobrazí seznam přidaných úkolů</t>
-  </si>
-  <si>
-    <t>V seznamu je alespoň 1 úkol</t>
-  </si>
-  <si>
-    <t>1. V hlavním menu zadejte 2 a potvrďte Enterem.</t>
-  </si>
-  <si>
-    <t>Program zobrazí nadpis Seznam úkolů: a všechny uložené úkoly s číslem, názvem a popisem.</t>
-  </si>
-  <si>
-    <t>TC03</t>
-  </si>
-  <si>
-    <t>Výběr volby 3 - odstranění úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že volba 3 zobrazí seznam úkolů a po zadání čísla úkol odstraní</t>
-  </si>
-  <si>
-    <t>1. V hlavním menu zadejte 3 a potvrďte Enterem. 
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funkce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Název</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstupní podmínky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroky testu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Očekávaný výsledek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skutečný výsledek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poznámky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hlavni_menu()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výběr volby 1 - přidání úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že volba 1 zobrazí výzvu k zadání úkolu a úkol je po vyplnění přidán do seznamu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">eznam úkolů je prázdný</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Zadejte 1 a potvrďte Enterem. 
+2. Zadejte název "Úkol 1". 
+3. Zadejte popis "Popis pro úkol 1". 
+4. Zvolte 2 pro zobrazení seznamu.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazí výzvu k zadání názvu a popisu. Po zadání zobrazí potvrzení Úkol </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Úkol 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> byl přidán. a úkol se objeví v seznamu.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Základní navigace z menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výběr volby 2 - zobrazení úkolů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že volba 2 zobrazí seznam přidaných úkolů</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu je alespoň 1 úkol</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. V hlavním menu zadejte 2 a potvrďte Enterem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program zobrazí nadpis Seznam úkolů: a všechny uložené úkoly s číslem, názvem a popisem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výběr volby 3 - odstranění úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že volba 3 zobrazí seznam úkolů a po zadání čísla úkol odstraní</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. V hlavním menu zadejte 3 a potvrďte Enterem. 
 2. Zadejte číslo 1 a potvrďte Enterem. 
 3. Zvolte 2 pro ověření.</t>
   </si>
   <si>
-    <t>Program zobrazí seznam úkolů, po zadání čísla zobrazí potvrzení Úkol '...' byl odstraněn. a úkol se již nezobrazí v seznamu.</t>
-  </si>
-  <si>
-    <t>TC04</t>
-  </si>
-  <si>
-    <t>Výběr volby 4 - konec programu</t>
-  </si>
-  <si>
-    <t>Ověření, že volba 4 zobrazí zprávu Konec programu. a program se ukončí</t>
-  </si>
-  <si>
-    <t>Program zobrazuje hlavní menu</t>
-  </si>
-  <si>
-    <t>1. Spusťte program. 
-2. Zadejte 4 a potvrďte Enterem.</t>
-  </si>
-  <si>
-    <t>Program zobrazí Konec programu. a ukončí se (přestane čekat na vstup).</t>
-  </si>
-  <si>
-    <t>TC05</t>
-  </si>
-  <si>
-    <t>Neplatná volba v menu</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání neplatné volby (mimo 1-4) zobrazí chybovou zprávu a menu se znovu zobrazí</t>
-  </si>
-  <si>
-    <t>1. Spusťte program. 
-2. Zadejte 5 a potvrďte Enterem. 
-3. Poté zadejte abc a potvrďte Enterem.</t>
-  </si>
-  <si>
-    <t>Program zobrazí upozornění „Neplatná volba" a znovu zobrazí hlavní menu</t>
-  </si>
-  <si>
-    <t>Hraniční případ - ověření odolnosti vůči neplatným vstupům</t>
-  </si>
-  <si>
-    <t>TC06</t>
-  </si>
-  <si>
-    <t>pridat_ukol()</t>
-  </si>
-  <si>
-    <t>Přidání úkolu s platnými vstupy</t>
-  </si>
-  <si>
-    <t>Ověření, že úkol s neprázdným názvem a popisem je úspěšně přidán do seznamu</t>
-  </si>
-  <si>
-    <t>Seznam ukoly je prázdný</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 1. 
+    <t xml:space="preserve">Program zobrazí seznam úkolů, po zadání čísla zobrazí potvrzení Úkol '...' byl odstraněn. a úkol se již nezobrazí v seznamu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výběr volby 4 - konec programu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že volba 4 zobrazí zprávu Konec programu. a program se ukončí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program zobrazuje hlavní menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Zadejte 4 a potvrďte Enterem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program zobrazí Konec programu. a ukončí se (přestane čekat na vstup).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neplatná volba v menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání neplatné volby (mimo 1-4) zobrazí chybovou zprávu a menu se znovu zobrazí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Zadejte 5 a potvrďte Enterem. 
+2. Poté zadejte abc a potvrďte Enterem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program zobrazí upozornění „Neplatná volba" a znovu zobrazí hlavní menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hraniční případ - ověření odolnosti vůči neplatným vstupům</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pridat_ukol()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Přidání úkolu s platnými vstupy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že úkol s neprázdným názvem a popisem je úspěšně přidán do seznamu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Z menu zvolte 1. 
 2. Zadejte název "Testování". 
-3. Zadejte popis "Napsat testovací případy".</t>
-  </si>
-  <si>
-    <t>Úkol je přidán a program zobrazí potvrzení. Po zvolení volby 2 se úkol zobrazí v seznamu.</t>
-  </si>
-  <si>
-    <t>Základní pozitivní test</t>
-  </si>
-  <si>
-    <t>TC07</t>
-  </si>
-  <si>
-    <t>Prázdný název úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání prázdného názvu zobrazí upozornění a vyžádá nový vstup</t>
-  </si>
-  <si>
-    <t>Program čeká na zadání názvu úkolu</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 1. 
+3. Zadejte popis "Napsat testovací případy".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">4. Zvolte 2 pro zobrazení seznamu.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Úkol je přidán a program zobrazí potvrzení. Po vybrání volby 2 se úkol zobrazí v seznamu s korektním číslem, názvem i popisem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Základní pozitivní test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prázdný název úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání prázdného názvu zobrazí upozornění a vyžádá nový vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 1. 
 2. Stiskněte Enter bez zadání textu.</t>
   </si>
   <si>
-    <t>Program zobrazí chybovou zprávu a znovu požádá o zadání názvu</t>
-  </si>
-  <si>
-    <t>Negativní test - prázdný název</t>
-  </si>
-  <si>
-    <t>TC08</t>
-  </si>
-  <si>
-    <t>Prázdný popis úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání prázdného popisu zobrazí upozornění a vyžádá nový vstup</t>
-  </si>
-  <si>
-    <t>Název úkolu byl již zadán platně</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 1. 
+    <t xml:space="preserve">Program zobrazí chybovou zprávu a znovu požádá o zadání názvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negativní test - prázdný název</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prázdný popis úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání prázdného popisu zobrazí upozornění a vyžádá nový vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 1. 
 2. Zadejte platný název. 
 3. Stiskněte Enter bez zadání popisu.</t>
   </si>
   <si>
-    <t>Program zobrazí chybovou zprávu a znovu požádá o zadání popisu</t>
-  </si>
-  <si>
-    <t>Negativní test - prázdný popis</t>
-  </si>
-  <si>
-    <t>TC09</t>
-  </si>
-  <si>
-    <t>Prázdný název i popis - opakované prázdné vstupy</t>
-  </si>
-  <si>
-    <t>Ověření, že při opakovaném zadávání prázdných hodnot program stále čeká na platný vstup</t>
-  </si>
-  <si>
-    <t>Program spuštěn, volba 1 zvolena</t>
-  </si>
-  <si>
-    <t>1. Stiskněte Enter 3× za sebou pro název. 
+    <t xml:space="preserve">Program zobrazí chybovou zprávu a znovu požádá o zadání popisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negativní test - prázdný popis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prázdný název i popis - opakované prázdné vstupy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že při opakovaném zadávání prázdných hodnot program stále čeká na platný vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program spuštěn, volba 1 zvolena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Stiskněte Enter 3× za sebou pro název. 
 2. Zadejte platný název. 
 3. Stiskněte Enter 3× za sebou pro popis. 
 4. Zadejte platný popis.</t>
   </si>
   <si>
-    <t>Program při každém prázdném vstupu zobrazí upozornění a čeká na platný vstup. Úkol je nakonec přidán.</t>
-  </si>
-  <si>
-    <t>Hraniční případ - odolnost vůči opakovaně prázdným vstupům</t>
-  </si>
-  <si>
-    <t>TC10</t>
-  </si>
-  <si>
-    <t>zobrazit_ukoly()</t>
-  </si>
-  <si>
-    <t>Zobrazení prázdného seznamu</t>
-  </si>
-  <si>
-    <t>Ověření, že při prázdném seznamu program zobrazí odpovídající zprávu</t>
-  </si>
-  <si>
-    <t>1. Spusťte program. 
+    <t xml:space="preserve">Program při každém prázdném vstupu zobrazí upozornění a čeká na platný vstup. Úkol je nakonec přidán.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hraniční případ - odolnost vůči opakovaně prázdným vstupům</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zobrazit_ukoly()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zobrazení prázdného seznamu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že při prázdném seznamu program zobrazí odpovídající zprávu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 2.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazí </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Seznam úkolů je prázdný."</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hraniční případ - prázdný seznam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zobrazení jednoho úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že je správně zobrazen jeden úkol v seznamu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">úkolů</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> je právě jeden úkol</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Program zobrazí seznam s jedním číslovaným úkolem (název a popis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zobrazení více úkolů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že jsou správně zobrazeny všechny úkoly v číslovaném pořadí</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu jsou alespoň 3 úkoly</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Přidejte 3 různé úkoly. 
 2. Z menu zvolte 2.</t>
   </si>
   <si>
-    <t>Program zobrazí „Seznam úkolů je prázdný."</t>
-  </si>
-  <si>
-    <t>Hraniční případ - prázdný seznam</t>
-  </si>
-  <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>Zobrazení jednoho úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že je správně zobrazen jeden úkol v seznamu</t>
-  </si>
-  <si>
-    <t>V seznamu ukoly je právě jeden úkol</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 2.</t>
-  </si>
-  <si>
-    <t>Program zobrazí seznam s jedním číslovaným úkolem (název a popis)</t>
-  </si>
-  <si>
-    <t>TC12</t>
-  </si>
-  <si>
-    <t>Zobrazení více úkolů</t>
-  </si>
-  <si>
-    <t>Ověření, že jsou správně zobrazeny všechny úkoly v číslovaném pořadí</t>
-  </si>
-  <si>
-    <t>V seznamu jsou alespoň 3 úkoly</t>
-  </si>
-  <si>
-    <t>1. Přidejte 3 různé úkoly. 
-2. Z menu zvolte 2.</t>
-  </si>
-  <si>
-    <t>Program zobrazí všechny 3 úkoly očíslované od 1 do 3 se správnými názvy a popisy</t>
-  </si>
-  <si>
-    <t>TC13</t>
-  </si>
-  <si>
-    <t>odstranit_ukol()</t>
-  </si>
-  <si>
-    <t>Odstranění platného úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání platného čísla úkolu úkol odstraní ze seznamu</t>
-  </si>
-  <si>
-    <t>V seznamu jsou alespoň 2 úkoly</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 3. 
+    <t xml:space="preserve">Program zobrazí všechny 3 úkoly očíslované od 1 do 3 se správnými názvy a popisy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">odstranit_ukol()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odstranění platného úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání platného čísla úkolu úkol odstraní ze seznamu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu jsou alespoň 2 úkoly</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 3. 
 2. Zadejte číslo 1 a potvrďte Enterem.</t>
   </si>
   <si>
-    <t>První úkol je odstraněn, program zobrazí potvrzení. Po volbě 2 se odstraněný úkol v seznamu již nezobrazí.</t>
-  </si>
-  <si>
-    <t>TC14</t>
-  </si>
-  <si>
-    <t>Číslo úkolu mimo rozsah - příliš velké</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání čísla většího než počet úkolů zobrazí upozornění</t>
-  </si>
-  <si>
-    <t>V seznamu jsou 2 úkoly</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 3. 
+    <t xml:space="preserve">První úkol je odstraněn, program zobrazí potvrzení. Po volbě 2 se odstraněný úkol v seznamu již nezobrazí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Číslo úkolu mimo rozsah - příliš velké</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání čísla většího než počet úkolů zobrazí upozornění</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu jsou 2 úkoly</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 3. 
 2. Zadejte číslo 99 a potvrďte Enterem.</t>
   </si>
   <si>
-    <t>Program zobrazí chybovou zprávu a čeká na nové číslo. Žádný úkol není odstraněn.</t>
-  </si>
-  <si>
-    <t>Negativní test - číslo mimo rozsah</t>
-  </si>
-  <si>
-    <t>TC15</t>
-  </si>
-  <si>
-    <t>Číslo úkolu mimo rozsah - nula nebo záporné</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání čísla 0 nebo záporného čísla zobrazí upozornění</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 3. 
+    <t xml:space="preserve">Program zobrazí chybovou zprávu a čeká na nové číslo. Žádný úkol není odstraněn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negativní test - číslo mimo rozsah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Číslo úkolu mimo rozsah - nula nebo záporné</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání čísla 0 nebo záporného čísla zobrazí upozornění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 3. 
 2. Zadejte 0. 
 3. Poté zadejte -5.</t>
   </si>
   <si>
-    <t>Program zobrazí chybovou zprávu pro každý neplatný vstup a čeká na platné číslo</t>
-  </si>
-  <si>
-    <t>Hraniční případ - hranice platného rozsahu</t>
-  </si>
-  <si>
-    <t>TC16</t>
-  </si>
-  <si>
-    <t>Nečíselný vstup při odstranění</t>
-  </si>
-  <si>
-    <t>Ověření, že zadání textu místo čísla zobrazí upozornění</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 3. 
-2. Zadejte abc a potvrďte Enterem.</t>
-  </si>
-  <si>
-    <t>Program zobrazí chybovou zprávu „Neplatný vstup. Zadejte celé číslo." a čeká na nový vstup</t>
-  </si>
-  <si>
-    <t>Negativní test - nečíselný vstup</t>
-  </si>
-  <si>
-    <t>TC17</t>
-  </si>
-  <si>
-    <t>Odstranění z prázdného seznamu</t>
-  </si>
-  <si>
-    <t>Ověření, že pokus o odstranění úkolu z prázdného seznamu zobrazí odpovídající zprávu</t>
-  </si>
-  <si>
-    <t>1. Z menu zvolte 3.</t>
-  </si>
-  <si>
-    <t>Program zobrazí „Seznam úkolů je prázdný, není co odstranit." a vrátí se do hlavního menu</t>
-  </si>
-  <si>
-    <t>TC18</t>
-  </si>
-  <si>
-    <t>Odstranění posledního úkolu</t>
-  </si>
-  <si>
-    <t>Ověření, že po odstranění posledního úkolu zůstane seznam prázdný</t>
-  </si>
-  <si>
-    <t>V seznamu je právě 1 úkol</t>
-  </si>
-  <si>
-    <t>1. Přidejte 1 úkol. 
+    <t xml:space="preserve">Program zobrazí chybovou zprávu pro každý neplatný vstup a čeká na platné číslo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hraniční případ - hranice platného rozsahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nečíselný vstup při odstranění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že zadání textu místo čísla zobrazí upozornění</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Z menu zvolte 3. 
+2. Zadejte </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">abc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> a potvrďte Enterem.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazí chybovou zprávu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Neplatný vstup. Zadejte celé číslo." a čeká na nový vstup</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Negativní test - nečíselný vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odstranění z prázdného seznamu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že pokus o odstranění úkolu z prázdného seznamu zobrazí odpovídající zprávu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Seznam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">úkolů</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> je prázdný</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Z menu zvolte 3.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazí </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Seznam úkolů je prázdný, není co odstranit.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> a vrátí se do hlavního menu</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TC18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odstranění posledního úkolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověření, že po odstranění posledního úkolu zůstane seznam prázdný</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Program zobrazuje hlavní menu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V seznamu je právě 1 úkol</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Přidejte 1 úkol. 
 2. Z menu zvolte 3. 
 3. Zadejte číslo 1. 
 4. Zvolte 2 pro zobrazení seznamu.</t>
   </si>
   <si>
-    <t>Úkol je odstraněn. Po volbě 2 program zobrazí „Seznam úkolů je prázdný."</t>
-  </si>
-  <si>
-    <t>Hraniční případ - odstranění posledního prvku</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Úkol je odstraněn. Po volbě 2 program zobrazí </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Seznam úkolů je prázdný.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hraniční případ - odstranění posledního prvku</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -449,74 +909,99 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,94 +1012,90 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -622,33 +1103,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -661,13 +1133,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -677,15 +1143,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -693,7 +1157,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -701,11 +1164,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -714,24 +1177,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.38"/>
-    <col customWidth="1" min="2" max="2" width="15.13"/>
-    <col customWidth="1" min="3" max="3" width="39.88"/>
-    <col customWidth="1" min="4" max="4" width="60.63"/>
-    <col customWidth="1" min="5" max="5" width="45.75"/>
-    <col customWidth="1" min="6" max="6" width="39.5"/>
-    <col customWidth="1" min="7" max="7" width="49.63"/>
-    <col customWidth="1" min="8" max="8" width="16.5"/>
-    <col customWidth="1" min="9" max="9" width="36.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="45.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="39.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="49.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36.63"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +1225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -770,16 +1235,16 @@
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="6" t="s">
@@ -789,7 +1254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -799,16 +1264,16 @@
       <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -816,7 +1281,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -826,16 +1291,16 @@
       <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="6" t="s">
@@ -843,7 +1308,7 @@
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -853,24 +1318,24 @@
       <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
@@ -880,26 +1345,26 @@
       <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
@@ -909,3313 +1374,3319 @@
       <c r="C7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="I8" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="I9" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="I14" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="I18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="I19" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115">
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139">
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140">
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155">
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158">
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159">
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160">
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161">
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162">
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163">
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164">
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165">
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166">
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167">
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168">
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169">
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170">
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171">
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172">
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173">
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174">
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175">
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176">
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177">
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178">
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179">
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180">
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181">
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182">
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183">
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184">
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185">
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186">
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187">
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188">
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189">
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190">
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191">
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192">
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193">
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194">
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195">
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196">
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197">
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198">
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199">
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200">
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
-    <row r="201">
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I201" s="7"/>
     </row>
-    <row r="202">
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I202" s="7"/>
     </row>
-    <row r="203">
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I203" s="7"/>
     </row>
-    <row r="204">
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I204" s="7"/>
     </row>
-    <row r="205">
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I205" s="7"/>
     </row>
-    <row r="206">
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I206" s="7"/>
     </row>
-    <row r="207">
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I207" s="7"/>
     </row>
-    <row r="208">
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I208" s="7"/>
     </row>
-    <row r="209">
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I209" s="7"/>
     </row>
-    <row r="210">
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I210" s="7"/>
     </row>
-    <row r="211">
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I211" s="7"/>
     </row>
-    <row r="212">
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I212" s="7"/>
     </row>
-    <row r="213">
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I213" s="7"/>
     </row>
-    <row r="214">
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I214" s="7"/>
     </row>
-    <row r="215">
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I215" s="7"/>
     </row>
-    <row r="216">
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I216" s="7"/>
     </row>
-    <row r="217">
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I217" s="7"/>
     </row>
-    <row r="218">
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I218" s="7"/>
     </row>
-    <row r="219">
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I219" s="7"/>
     </row>
-    <row r="220">
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I220" s="7"/>
     </row>
-    <row r="221">
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I221" s="7"/>
     </row>
-    <row r="222">
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I222" s="7"/>
     </row>
-    <row r="223">
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I223" s="7"/>
     </row>
-    <row r="224">
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I224" s="7"/>
     </row>
-    <row r="225">
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I225" s="7"/>
     </row>
-    <row r="226">
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I226" s="7"/>
     </row>
-    <row r="227">
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I227" s="7"/>
     </row>
-    <row r="228">
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I228" s="7"/>
     </row>
-    <row r="229">
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I229" s="7"/>
     </row>
-    <row r="230">
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I230" s="7"/>
     </row>
-    <row r="231">
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I231" s="7"/>
     </row>
-    <row r="232">
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I232" s="7"/>
     </row>
-    <row r="233">
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I233" s="7"/>
     </row>
-    <row r="234">
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I234" s="7"/>
     </row>
-    <row r="235">
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I235" s="7"/>
     </row>
-    <row r="236">
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I236" s="7"/>
     </row>
-    <row r="237">
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I237" s="7"/>
     </row>
-    <row r="238">
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I238" s="7"/>
     </row>
-    <row r="239">
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I239" s="7"/>
     </row>
-    <row r="240">
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I240" s="7"/>
     </row>
-    <row r="241">
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I241" s="7"/>
     </row>
-    <row r="242">
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I242" s="7"/>
     </row>
-    <row r="243">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I243" s="7"/>
     </row>
-    <row r="244">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I244" s="7"/>
     </row>
-    <row r="245">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I245" s="7"/>
     </row>
-    <row r="246">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I246" s="7"/>
     </row>
-    <row r="247">
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I247" s="7"/>
     </row>
-    <row r="248">
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I248" s="7"/>
     </row>
-    <row r="249">
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I249" s="7"/>
     </row>
-    <row r="250">
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I250" s="7"/>
     </row>
-    <row r="251">
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I251" s="7"/>
     </row>
-    <row r="252">
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I252" s="7"/>
     </row>
-    <row r="253">
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I253" s="7"/>
     </row>
-    <row r="254">
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I254" s="7"/>
     </row>
-    <row r="255">
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I255" s="7"/>
     </row>
-    <row r="256">
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I256" s="7"/>
     </row>
-    <row r="257">
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I257" s="7"/>
     </row>
-    <row r="258">
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I258" s="7"/>
     </row>
-    <row r="259">
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I259" s="7"/>
     </row>
-    <row r="260">
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I260" s="7"/>
     </row>
-    <row r="261">
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I261" s="7"/>
     </row>
-    <row r="262">
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I262" s="7"/>
     </row>
-    <row r="263">
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I263" s="7"/>
     </row>
-    <row r="264">
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I264" s="7"/>
     </row>
-    <row r="265">
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I265" s="7"/>
     </row>
-    <row r="266">
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I266" s="7"/>
     </row>
-    <row r="267">
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I267" s="7"/>
     </row>
-    <row r="268">
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I268" s="7"/>
     </row>
-    <row r="269">
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I269" s="7"/>
     </row>
-    <row r="270">
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I270" s="7"/>
     </row>
-    <row r="271">
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I271" s="7"/>
     </row>
-    <row r="272">
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I272" s="7"/>
     </row>
-    <row r="273">
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I273" s="7"/>
     </row>
-    <row r="274">
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I274" s="7"/>
     </row>
-    <row r="275">
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I275" s="7"/>
     </row>
-    <row r="276">
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I276" s="7"/>
     </row>
-    <row r="277">
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I277" s="7"/>
     </row>
-    <row r="278">
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I278" s="7"/>
     </row>
-    <row r="279">
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I279" s="7"/>
     </row>
-    <row r="280">
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I280" s="7"/>
     </row>
-    <row r="281">
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I281" s="7"/>
     </row>
-    <row r="282">
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I282" s="7"/>
     </row>
-    <row r="283">
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I283" s="7"/>
     </row>
-    <row r="284">
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I284" s="7"/>
     </row>
-    <row r="285">
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I285" s="7"/>
     </row>
-    <row r="286">
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I286" s="7"/>
     </row>
-    <row r="287">
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I287" s="7"/>
     </row>
-    <row r="288">
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I288" s="7"/>
     </row>
-    <row r="289">
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I289" s="7"/>
     </row>
-    <row r="290">
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I290" s="7"/>
     </row>
-    <row r="291">
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I291" s="7"/>
     </row>
-    <row r="292">
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I292" s="7"/>
     </row>
-    <row r="293">
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I293" s="7"/>
     </row>
-    <row r="294">
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I294" s="7"/>
     </row>
-    <row r="295">
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I295" s="7"/>
     </row>
-    <row r="296">
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I296" s="7"/>
     </row>
-    <row r="297">
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I297" s="7"/>
     </row>
-    <row r="298">
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I298" s="7"/>
     </row>
-    <row r="299">
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I299" s="7"/>
     </row>
-    <row r="300">
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I300" s="7"/>
     </row>
-    <row r="301">
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I301" s="7"/>
     </row>
-    <row r="302">
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I302" s="7"/>
     </row>
-    <row r="303">
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I303" s="7"/>
     </row>
-    <row r="304">
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I304" s="7"/>
     </row>
-    <row r="305">
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I305" s="7"/>
     </row>
-    <row r="306">
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I306" s="7"/>
     </row>
-    <row r="307">
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I307" s="7"/>
     </row>
-    <row r="308">
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I308" s="7"/>
     </row>
-    <row r="309">
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I309" s="7"/>
     </row>
-    <row r="310">
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I310" s="7"/>
     </row>
-    <row r="311">
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I311" s="7"/>
     </row>
-    <row r="312">
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I312" s="7"/>
     </row>
-    <row r="313">
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I313" s="7"/>
     </row>
-    <row r="314">
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I314" s="7"/>
     </row>
-    <row r="315">
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I315" s="7"/>
     </row>
-    <row r="316">
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I316" s="7"/>
     </row>
-    <row r="317">
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I317" s="7"/>
     </row>
-    <row r="318">
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I318" s="7"/>
     </row>
-    <row r="319">
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I319" s="7"/>
     </row>
-    <row r="320">
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I320" s="7"/>
     </row>
-    <row r="321">
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I321" s="7"/>
     </row>
-    <row r="322">
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I322" s="7"/>
     </row>
-    <row r="323">
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I323" s="7"/>
     </row>
-    <row r="324">
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I324" s="7"/>
     </row>
-    <row r="325">
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I325" s="7"/>
     </row>
-    <row r="326">
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I326" s="7"/>
     </row>
-    <row r="327">
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I327" s="7"/>
     </row>
-    <row r="328">
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I328" s="7"/>
     </row>
-    <row r="329">
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I329" s="7"/>
     </row>
-    <row r="330">
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I330" s="7"/>
     </row>
-    <row r="331">
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I331" s="7"/>
     </row>
-    <row r="332">
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I332" s="7"/>
     </row>
-    <row r="333">
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I333" s="7"/>
     </row>
-    <row r="334">
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I334" s="7"/>
     </row>
-    <row r="335">
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I335" s="7"/>
     </row>
-    <row r="336">
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I336" s="7"/>
     </row>
-    <row r="337">
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I337" s="7"/>
     </row>
-    <row r="338">
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I338" s="7"/>
     </row>
-    <row r="339">
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I339" s="7"/>
     </row>
-    <row r="340">
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I340" s="7"/>
     </row>
-    <row r="341">
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I341" s="7"/>
     </row>
-    <row r="342">
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I342" s="7"/>
     </row>
-    <row r="343">
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I343" s="7"/>
     </row>
-    <row r="344">
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I344" s="7"/>
     </row>
-    <row r="345">
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I345" s="7"/>
     </row>
-    <row r="346">
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I346" s="7"/>
     </row>
-    <row r="347">
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I347" s="7"/>
     </row>
-    <row r="348">
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I348" s="7"/>
     </row>
-    <row r="349">
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I349" s="7"/>
     </row>
-    <row r="350">
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I350" s="7"/>
     </row>
-    <row r="351">
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I351" s="7"/>
     </row>
-    <row r="352">
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I352" s="7"/>
     </row>
-    <row r="353">
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I353" s="7"/>
     </row>
-    <row r="354">
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I354" s="7"/>
     </row>
-    <row r="355">
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I355" s="7"/>
     </row>
-    <row r="356">
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I356" s="7"/>
     </row>
-    <row r="357">
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I357" s="7"/>
     </row>
-    <row r="358">
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I358" s="7"/>
     </row>
-    <row r="359">
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I359" s="7"/>
     </row>
-    <row r="360">
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I360" s="7"/>
     </row>
-    <row r="361">
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I361" s="7"/>
     </row>
-    <row r="362">
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I362" s="7"/>
     </row>
-    <row r="363">
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I363" s="7"/>
     </row>
-    <row r="364">
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I364" s="7"/>
     </row>
-    <row r="365">
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I365" s="7"/>
     </row>
-    <row r="366">
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I366" s="7"/>
     </row>
-    <row r="367">
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I367" s="7"/>
     </row>
-    <row r="368">
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I368" s="7"/>
     </row>
-    <row r="369">
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I369" s="7"/>
     </row>
-    <row r="370">
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I370" s="7"/>
     </row>
-    <row r="371">
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I371" s="7"/>
     </row>
-    <row r="372">
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I372" s="7"/>
     </row>
-    <row r="373">
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I373" s="7"/>
     </row>
-    <row r="374">
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I374" s="7"/>
     </row>
-    <row r="375">
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I375" s="7"/>
     </row>
-    <row r="376">
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I376" s="7"/>
     </row>
-    <row r="377">
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I377" s="7"/>
     </row>
-    <row r="378">
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I378" s="7"/>
     </row>
-    <row r="379">
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I379" s="7"/>
     </row>
-    <row r="380">
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I380" s="7"/>
     </row>
-    <row r="381">
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I381" s="7"/>
     </row>
-    <row r="382">
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I382" s="7"/>
     </row>
-    <row r="383">
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I383" s="7"/>
     </row>
-    <row r="384">
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I384" s="7"/>
     </row>
-    <row r="385">
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I385" s="7"/>
     </row>
-    <row r="386">
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I386" s="7"/>
     </row>
-    <row r="387">
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I387" s="7"/>
     </row>
-    <row r="388">
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I388" s="7"/>
     </row>
-    <row r="389">
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I389" s="7"/>
     </row>
-    <row r="390">
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I390" s="7"/>
     </row>
-    <row r="391">
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I391" s="7"/>
     </row>
-    <row r="392">
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I392" s="7"/>
     </row>
-    <row r="393">
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I393" s="7"/>
     </row>
-    <row r="394">
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I394" s="7"/>
     </row>
-    <row r="395">
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I395" s="7"/>
     </row>
-    <row r="396">
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I396" s="7"/>
     </row>
-    <row r="397">
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I397" s="7"/>
     </row>
-    <row r="398">
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I398" s="7"/>
     </row>
-    <row r="399">
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I399" s="7"/>
     </row>
-    <row r="400">
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I400" s="7"/>
     </row>
-    <row r="401">
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I401" s="7"/>
     </row>
-    <row r="402">
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I402" s="7"/>
     </row>
-    <row r="403">
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I403" s="7"/>
     </row>
-    <row r="404">
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I404" s="7"/>
     </row>
-    <row r="405">
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I405" s="7"/>
     </row>
-    <row r="406">
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I406" s="7"/>
     </row>
-    <row r="407">
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I407" s="7"/>
     </row>
-    <row r="408">
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I408" s="7"/>
     </row>
-    <row r="409">
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I409" s="7"/>
     </row>
-    <row r="410">
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I410" s="7"/>
     </row>
-    <row r="411">
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I411" s="7"/>
     </row>
-    <row r="412">
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I412" s="7"/>
     </row>
-    <row r="413">
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I413" s="7"/>
     </row>
-    <row r="414">
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I414" s="7"/>
     </row>
-    <row r="415">
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I415" s="7"/>
     </row>
-    <row r="416">
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I416" s="7"/>
     </row>
-    <row r="417">
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I417" s="7"/>
     </row>
-    <row r="418">
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I418" s="7"/>
     </row>
-    <row r="419">
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I419" s="7"/>
     </row>
-    <row r="420">
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I420" s="7"/>
     </row>
-    <row r="421">
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I421" s="7"/>
     </row>
-    <row r="422">
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I422" s="7"/>
     </row>
-    <row r="423">
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I423" s="7"/>
     </row>
-    <row r="424">
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I424" s="7"/>
     </row>
-    <row r="425">
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I425" s="7"/>
     </row>
-    <row r="426">
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I426" s="7"/>
     </row>
-    <row r="427">
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I427" s="7"/>
     </row>
-    <row r="428">
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I428" s="7"/>
     </row>
-    <row r="429">
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I429" s="7"/>
     </row>
-    <row r="430">
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I430" s="7"/>
     </row>
-    <row r="431">
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I431" s="7"/>
     </row>
-    <row r="432">
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I432" s="7"/>
     </row>
-    <row r="433">
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I433" s="7"/>
     </row>
-    <row r="434">
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I434" s="7"/>
     </row>
-    <row r="435">
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I435" s="7"/>
     </row>
-    <row r="436">
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I436" s="7"/>
     </row>
-    <row r="437">
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I437" s="7"/>
     </row>
-    <row r="438">
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I438" s="7"/>
     </row>
-    <row r="439">
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I439" s="7"/>
     </row>
-    <row r="440">
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I440" s="7"/>
     </row>
-    <row r="441">
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I441" s="7"/>
     </row>
-    <row r="442">
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I442" s="7"/>
     </row>
-    <row r="443">
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I443" s="7"/>
     </row>
-    <row r="444">
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I444" s="7"/>
     </row>
-    <row r="445">
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I445" s="7"/>
     </row>
-    <row r="446">
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I446" s="7"/>
     </row>
-    <row r="447">
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I447" s="7"/>
     </row>
-    <row r="448">
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I448" s="7"/>
     </row>
-    <row r="449">
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I449" s="7"/>
     </row>
-    <row r="450">
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I450" s="7"/>
     </row>
-    <row r="451">
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I451" s="7"/>
     </row>
-    <row r="452">
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I452" s="7"/>
     </row>
-    <row r="453">
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I453" s="7"/>
     </row>
-    <row r="454">
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I454" s="7"/>
     </row>
-    <row r="455">
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I455" s="7"/>
     </row>
-    <row r="456">
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I456" s="7"/>
     </row>
-    <row r="457">
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I457" s="7"/>
     </row>
-    <row r="458">
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I458" s="7"/>
     </row>
-    <row r="459">
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I459" s="7"/>
     </row>
-    <row r="460">
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I460" s="7"/>
     </row>
-    <row r="461">
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I461" s="7"/>
     </row>
-    <row r="462">
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I462" s="7"/>
     </row>
-    <row r="463">
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I463" s="7"/>
     </row>
-    <row r="464">
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I464" s="7"/>
     </row>
-    <row r="465">
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I465" s="7"/>
     </row>
-    <row r="466">
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I466" s="7"/>
     </row>
-    <row r="467">
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I467" s="7"/>
     </row>
-    <row r="468">
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I468" s="7"/>
     </row>
-    <row r="469">
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I469" s="7"/>
     </row>
-    <row r="470">
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I470" s="7"/>
     </row>
-    <row r="471">
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I471" s="7"/>
     </row>
-    <row r="472">
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I472" s="7"/>
     </row>
-    <row r="473">
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I473" s="7"/>
     </row>
-    <row r="474">
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I474" s="7"/>
     </row>
-    <row r="475">
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I475" s="7"/>
     </row>
-    <row r="476">
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I476" s="7"/>
     </row>
-    <row r="477">
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I477" s="7"/>
     </row>
-    <row r="478">
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I478" s="7"/>
     </row>
-    <row r="479">
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I479" s="7"/>
     </row>
-    <row r="480">
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I480" s="7"/>
     </row>
-    <row r="481">
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I481" s="7"/>
     </row>
-    <row r="482">
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I482" s="7"/>
     </row>
-    <row r="483">
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I483" s="7"/>
     </row>
-    <row r="484">
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I484" s="7"/>
     </row>
-    <row r="485">
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I485" s="7"/>
     </row>
-    <row r="486">
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I486" s="7"/>
     </row>
-    <row r="487">
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I487" s="7"/>
     </row>
-    <row r="488">
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I488" s="7"/>
     </row>
-    <row r="489">
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I489" s="7"/>
     </row>
-    <row r="490">
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I490" s="7"/>
     </row>
-    <row r="491">
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I491" s="7"/>
     </row>
-    <row r="492">
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I492" s="7"/>
     </row>
-    <row r="493">
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I493" s="7"/>
     </row>
-    <row r="494">
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I494" s="7"/>
     </row>
-    <row r="495">
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I495" s="7"/>
     </row>
-    <row r="496">
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I496" s="7"/>
     </row>
-    <row r="497">
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I497" s="7"/>
     </row>
-    <row r="498">
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I498" s="7"/>
     </row>
-    <row r="499">
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I499" s="7"/>
     </row>
-    <row r="500">
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I500" s="7"/>
     </row>
-    <row r="501">
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I501" s="7"/>
     </row>
-    <row r="502">
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I502" s="7"/>
     </row>
-    <row r="503">
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I503" s="7"/>
     </row>
-    <row r="504">
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I504" s="7"/>
     </row>
-    <row r="505">
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I505" s="7"/>
     </row>
-    <row r="506">
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I506" s="7"/>
     </row>
-    <row r="507">
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I507" s="7"/>
     </row>
-    <row r="508">
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I508" s="7"/>
     </row>
-    <row r="509">
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I509" s="7"/>
     </row>
-    <row r="510">
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I510" s="7"/>
     </row>
-    <row r="511">
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I511" s="7"/>
     </row>
-    <row r="512">
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I512" s="7"/>
     </row>
-    <row r="513">
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I513" s="7"/>
     </row>
-    <row r="514">
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I514" s="7"/>
     </row>
-    <row r="515">
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I515" s="7"/>
     </row>
-    <row r="516">
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I516" s="7"/>
     </row>
-    <row r="517">
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I517" s="7"/>
     </row>
-    <row r="518">
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I518" s="7"/>
     </row>
-    <row r="519">
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I519" s="7"/>
     </row>
-    <row r="520">
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I520" s="7"/>
     </row>
-    <row r="521">
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I521" s="7"/>
     </row>
-    <row r="522">
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I522" s="7"/>
     </row>
-    <row r="523">
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I523" s="7"/>
     </row>
-    <row r="524">
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I524" s="7"/>
     </row>
-    <row r="525">
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I525" s="7"/>
     </row>
-    <row r="526">
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I526" s="7"/>
     </row>
-    <row r="527">
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I527" s="7"/>
     </row>
-    <row r="528">
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I528" s="7"/>
     </row>
-    <row r="529">
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I529" s="7"/>
     </row>
-    <row r="530">
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I530" s="7"/>
     </row>
-    <row r="531">
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I531" s="7"/>
     </row>
-    <row r="532">
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I532" s="7"/>
     </row>
-    <row r="533">
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I533" s="7"/>
     </row>
-    <row r="534">
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I534" s="7"/>
     </row>
-    <row r="535">
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I535" s="7"/>
     </row>
-    <row r="536">
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I536" s="7"/>
     </row>
-    <row r="537">
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I537" s="7"/>
     </row>
-    <row r="538">
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I538" s="7"/>
     </row>
-    <row r="539">
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I539" s="7"/>
     </row>
-    <row r="540">
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I540" s="7"/>
     </row>
-    <row r="541">
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I541" s="7"/>
     </row>
-    <row r="542">
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I542" s="7"/>
     </row>
-    <row r="543">
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I543" s="7"/>
     </row>
-    <row r="544">
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I544" s="7"/>
     </row>
-    <row r="545">
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I545" s="7"/>
     </row>
-    <row r="546">
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I546" s="7"/>
     </row>
-    <row r="547">
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I547" s="7"/>
     </row>
-    <row r="548">
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I548" s="7"/>
     </row>
-    <row r="549">
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I549" s="7"/>
     </row>
-    <row r="550">
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I550" s="7"/>
     </row>
-    <row r="551">
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I551" s="7"/>
     </row>
-    <row r="552">
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I552" s="7"/>
     </row>
-    <row r="553">
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I553" s="7"/>
     </row>
-    <row r="554">
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I554" s="7"/>
     </row>
-    <row r="555">
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I555" s="7"/>
     </row>
-    <row r="556">
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I556" s="7"/>
     </row>
-    <row r="557">
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I557" s="7"/>
     </row>
-    <row r="558">
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I558" s="7"/>
     </row>
-    <row r="559">
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I559" s="7"/>
     </row>
-    <row r="560">
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I560" s="7"/>
     </row>
-    <row r="561">
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I561" s="7"/>
     </row>
-    <row r="562">
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I562" s="7"/>
     </row>
-    <row r="563">
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I563" s="7"/>
     </row>
-    <row r="564">
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I564" s="7"/>
     </row>
-    <row r="565">
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I565" s="7"/>
     </row>
-    <row r="566">
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I566" s="7"/>
     </row>
-    <row r="567">
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I567" s="7"/>
     </row>
-    <row r="568">
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I568" s="7"/>
     </row>
-    <row r="569">
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I569" s="7"/>
     </row>
-    <row r="570">
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I570" s="7"/>
     </row>
-    <row r="571">
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I571" s="7"/>
     </row>
-    <row r="572">
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I572" s="7"/>
     </row>
-    <row r="573">
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I573" s="7"/>
     </row>
-    <row r="574">
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I574" s="7"/>
     </row>
-    <row r="575">
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I575" s="7"/>
     </row>
-    <row r="576">
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I576" s="7"/>
     </row>
-    <row r="577">
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I577" s="7"/>
     </row>
-    <row r="578">
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I578" s="7"/>
     </row>
-    <row r="579">
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I579" s="7"/>
     </row>
-    <row r="580">
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I580" s="7"/>
     </row>
-    <row r="581">
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I581" s="7"/>
     </row>
-    <row r="582">
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I582" s="7"/>
     </row>
-    <row r="583">
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I583" s="7"/>
     </row>
-    <row r="584">
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I584" s="7"/>
     </row>
-    <row r="585">
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I585" s="7"/>
     </row>
-    <row r="586">
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I586" s="7"/>
     </row>
-    <row r="587">
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I587" s="7"/>
     </row>
-    <row r="588">
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I588" s="7"/>
     </row>
-    <row r="589">
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I589" s="7"/>
     </row>
-    <row r="590">
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I590" s="7"/>
     </row>
-    <row r="591">
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I591" s="7"/>
     </row>
-    <row r="592">
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I592" s="7"/>
     </row>
-    <row r="593">
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I593" s="7"/>
     </row>
-    <row r="594">
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I594" s="7"/>
     </row>
-    <row r="595">
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I595" s="7"/>
     </row>
-    <row r="596">
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I596" s="7"/>
     </row>
-    <row r="597">
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I597" s="7"/>
     </row>
-    <row r="598">
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I598" s="7"/>
     </row>
-    <row r="599">
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I599" s="7"/>
     </row>
-    <row r="600">
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I600" s="7"/>
     </row>
-    <row r="601">
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I601" s="7"/>
     </row>
-    <row r="602">
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I602" s="7"/>
     </row>
-    <row r="603">
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I603" s="7"/>
     </row>
-    <row r="604">
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I604" s="7"/>
     </row>
-    <row r="605">
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I605" s="7"/>
     </row>
-    <row r="606">
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I606" s="7"/>
     </row>
-    <row r="607">
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I607" s="7"/>
     </row>
-    <row r="608">
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I608" s="7"/>
     </row>
-    <row r="609">
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I609" s="7"/>
     </row>
-    <row r="610">
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I610" s="7"/>
     </row>
-    <row r="611">
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I611" s="7"/>
     </row>
-    <row r="612">
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I612" s="7"/>
     </row>
-    <row r="613">
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I613" s="7"/>
     </row>
-    <row r="614">
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I614" s="7"/>
     </row>
-    <row r="615">
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I615" s="7"/>
     </row>
-    <row r="616">
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I616" s="7"/>
     </row>
-    <row r="617">
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I617" s="7"/>
     </row>
-    <row r="618">
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I618" s="7"/>
     </row>
-    <row r="619">
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I619" s="7"/>
     </row>
-    <row r="620">
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I620" s="7"/>
     </row>
-    <row r="621">
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I621" s="7"/>
     </row>
-    <row r="622">
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I622" s="7"/>
     </row>
-    <row r="623">
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I623" s="7"/>
     </row>
-    <row r="624">
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I624" s="7"/>
     </row>
-    <row r="625">
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I625" s="7"/>
     </row>
-    <row r="626">
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I626" s="7"/>
     </row>
-    <row r="627">
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I627" s="7"/>
     </row>
-    <row r="628">
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I628" s="7"/>
     </row>
-    <row r="629">
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I629" s="7"/>
     </row>
-    <row r="630">
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I630" s="7"/>
     </row>
-    <row r="631">
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I631" s="7"/>
     </row>
-    <row r="632">
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I632" s="7"/>
     </row>
-    <row r="633">
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I633" s="7"/>
     </row>
-    <row r="634">
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I634" s="7"/>
     </row>
-    <row r="635">
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I635" s="7"/>
     </row>
-    <row r="636">
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I636" s="7"/>
     </row>
-    <row r="637">
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I637" s="7"/>
     </row>
-    <row r="638">
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I638" s="7"/>
     </row>
-    <row r="639">
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I639" s="7"/>
     </row>
-    <row r="640">
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I640" s="7"/>
     </row>
-    <row r="641">
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I641" s="7"/>
     </row>
-    <row r="642">
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I642" s="7"/>
     </row>
-    <row r="643">
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I643" s="7"/>
     </row>
-    <row r="644">
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I644" s="7"/>
     </row>
-    <row r="645">
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I645" s="7"/>
     </row>
-    <row r="646">
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I646" s="7"/>
     </row>
-    <row r="647">
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I647" s="7"/>
     </row>
-    <row r="648">
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I648" s="7"/>
     </row>
-    <row r="649">
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I649" s="7"/>
     </row>
-    <row r="650">
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I650" s="7"/>
     </row>
-    <row r="651">
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I651" s="7"/>
     </row>
-    <row r="652">
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I652" s="7"/>
     </row>
-    <row r="653">
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I653" s="7"/>
     </row>
-    <row r="654">
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I654" s="7"/>
     </row>
-    <row r="655">
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I655" s="7"/>
     </row>
-    <row r="656">
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I656" s="7"/>
     </row>
-    <row r="657">
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I657" s="7"/>
     </row>
-    <row r="658">
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I658" s="7"/>
     </row>
-    <row r="659">
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I659" s="7"/>
     </row>
-    <row r="660">
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I660" s="7"/>
     </row>
-    <row r="661">
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I661" s="7"/>
     </row>
-    <row r="662">
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I662" s="7"/>
     </row>
-    <row r="663">
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I663" s="7"/>
     </row>
-    <row r="664">
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I664" s="7"/>
     </row>
-    <row r="665">
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I665" s="7"/>
     </row>
-    <row r="666">
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I666" s="7"/>
     </row>
-    <row r="667">
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I667" s="7"/>
     </row>
-    <row r="668">
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I668" s="7"/>
     </row>
-    <row r="669">
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I669" s="7"/>
     </row>
-    <row r="670">
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I670" s="7"/>
     </row>
-    <row r="671">
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I671" s="7"/>
     </row>
-    <row r="672">
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I672" s="7"/>
     </row>
-    <row r="673">
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I673" s="7"/>
     </row>
-    <row r="674">
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I674" s="7"/>
     </row>
-    <row r="675">
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I675" s="7"/>
     </row>
-    <row r="676">
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I676" s="7"/>
     </row>
-    <row r="677">
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I677" s="7"/>
     </row>
-    <row r="678">
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I678" s="7"/>
     </row>
-    <row r="679">
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I679" s="7"/>
     </row>
-    <row r="680">
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I680" s="7"/>
     </row>
-    <row r="681">
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I681" s="7"/>
     </row>
-    <row r="682">
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I682" s="7"/>
     </row>
-    <row r="683">
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I683" s="7"/>
     </row>
-    <row r="684">
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I684" s="7"/>
     </row>
-    <row r="685">
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I685" s="7"/>
     </row>
-    <row r="686">
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I686" s="7"/>
     </row>
-    <row r="687">
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I687" s="7"/>
     </row>
-    <row r="688">
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I688" s="7"/>
     </row>
-    <row r="689">
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I689" s="7"/>
     </row>
-    <row r="690">
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I690" s="7"/>
     </row>
-    <row r="691">
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I691" s="7"/>
     </row>
-    <row r="692">
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I692" s="7"/>
     </row>
-    <row r="693">
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I693" s="7"/>
     </row>
-    <row r="694">
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I694" s="7"/>
     </row>
-    <row r="695">
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I695" s="7"/>
     </row>
-    <row r="696">
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I696" s="7"/>
     </row>
-    <row r="697">
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I697" s="7"/>
     </row>
-    <row r="698">
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I698" s="7"/>
     </row>
-    <row r="699">
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I699" s="7"/>
     </row>
-    <row r="700">
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I700" s="7"/>
     </row>
-    <row r="701">
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I701" s="7"/>
     </row>
-    <row r="702">
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I702" s="7"/>
     </row>
-    <row r="703">
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I703" s="7"/>
     </row>
-    <row r="704">
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I704" s="7"/>
     </row>
-    <row r="705">
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I705" s="7"/>
     </row>
-    <row r="706">
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I706" s="7"/>
     </row>
-    <row r="707">
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I707" s="7"/>
     </row>
-    <row r="708">
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I708" s="7"/>
     </row>
-    <row r="709">
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I709" s="7"/>
     </row>
-    <row r="710">
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I710" s="7"/>
     </row>
-    <row r="711">
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I711" s="7"/>
     </row>
-    <row r="712">
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I712" s="7"/>
     </row>
-    <row r="713">
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I713" s="7"/>
     </row>
-    <row r="714">
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I714" s="7"/>
     </row>
-    <row r="715">
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I715" s="7"/>
     </row>
-    <row r="716">
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I716" s="7"/>
     </row>
-    <row r="717">
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I717" s="7"/>
     </row>
-    <row r="718">
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I718" s="7"/>
     </row>
-    <row r="719">
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I719" s="7"/>
     </row>
-    <row r="720">
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I720" s="7"/>
     </row>
-    <row r="721">
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I721" s="7"/>
     </row>
-    <row r="722">
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I722" s="7"/>
     </row>
-    <row r="723">
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I723" s="7"/>
     </row>
-    <row r="724">
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I724" s="7"/>
     </row>
-    <row r="725">
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I725" s="7"/>
     </row>
-    <row r="726">
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I726" s="7"/>
     </row>
-    <row r="727">
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I727" s="7"/>
     </row>
-    <row r="728">
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I728" s="7"/>
     </row>
-    <row r="729">
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I729" s="7"/>
     </row>
-    <row r="730">
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I730" s="7"/>
     </row>
-    <row r="731">
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I731" s="7"/>
     </row>
-    <row r="732">
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I732" s="7"/>
     </row>
-    <row r="733">
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I733" s="7"/>
     </row>
-    <row r="734">
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I734" s="7"/>
     </row>
-    <row r="735">
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I735" s="7"/>
     </row>
-    <row r="736">
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I736" s="7"/>
     </row>
-    <row r="737">
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I737" s="7"/>
     </row>
-    <row r="738">
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I738" s="7"/>
     </row>
-    <row r="739">
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I739" s="7"/>
     </row>
-    <row r="740">
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I740" s="7"/>
     </row>
-    <row r="741">
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I741" s="7"/>
     </row>
-    <row r="742">
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I742" s="7"/>
     </row>
-    <row r="743">
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I743" s="7"/>
     </row>
-    <row r="744">
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I744" s="7"/>
     </row>
-    <row r="745">
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I745" s="7"/>
     </row>
-    <row r="746">
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I746" s="7"/>
     </row>
-    <row r="747">
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I747" s="7"/>
     </row>
-    <row r="748">
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I748" s="7"/>
     </row>
-    <row r="749">
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I749" s="7"/>
     </row>
-    <row r="750">
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I750" s="7"/>
     </row>
-    <row r="751">
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I751" s="7"/>
     </row>
-    <row r="752">
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I752" s="7"/>
     </row>
-    <row r="753">
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I753" s="7"/>
     </row>
-    <row r="754">
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I754" s="7"/>
     </row>
-    <row r="755">
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I755" s="7"/>
     </row>
-    <row r="756">
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I756" s="7"/>
     </row>
-    <row r="757">
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I757" s="7"/>
     </row>
-    <row r="758">
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I758" s="7"/>
     </row>
-    <row r="759">
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I759" s="7"/>
     </row>
-    <row r="760">
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I760" s="7"/>
     </row>
-    <row r="761">
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I761" s="7"/>
     </row>
-    <row r="762">
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I762" s="7"/>
     </row>
-    <row r="763">
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I763" s="7"/>
     </row>
-    <row r="764">
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I764" s="7"/>
     </row>
-    <row r="765">
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I765" s="7"/>
     </row>
-    <row r="766">
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I766" s="7"/>
     </row>
-    <row r="767">
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I767" s="7"/>
     </row>
-    <row r="768">
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I768" s="7"/>
     </row>
-    <row r="769">
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I769" s="7"/>
     </row>
-    <row r="770">
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I770" s="7"/>
     </row>
-    <row r="771">
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I771" s="7"/>
     </row>
-    <row r="772">
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I772" s="7"/>
     </row>
-    <row r="773">
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I773" s="7"/>
     </row>
-    <row r="774">
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I774" s="7"/>
     </row>
-    <row r="775">
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I775" s="7"/>
     </row>
-    <row r="776">
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I776" s="7"/>
     </row>
-    <row r="777">
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I777" s="7"/>
     </row>
-    <row r="778">
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I778" s="7"/>
     </row>
-    <row r="779">
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I779" s="7"/>
     </row>
-    <row r="780">
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I780" s="7"/>
     </row>
-    <row r="781">
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I781" s="7"/>
     </row>
-    <row r="782">
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I782" s="7"/>
     </row>
-    <row r="783">
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I783" s="7"/>
     </row>
-    <row r="784">
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I784" s="7"/>
     </row>
-    <row r="785">
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I785" s="7"/>
     </row>
-    <row r="786">
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I786" s="7"/>
     </row>
-    <row r="787">
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I787" s="7"/>
     </row>
-    <row r="788">
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I788" s="7"/>
     </row>
-    <row r="789">
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I789" s="7"/>
     </row>
-    <row r="790">
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I790" s="7"/>
     </row>
-    <row r="791">
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I791" s="7"/>
     </row>
-    <row r="792">
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I792" s="7"/>
     </row>
-    <row r="793">
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I793" s="7"/>
     </row>
-    <row r="794">
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I794" s="7"/>
     </row>
-    <row r="795">
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I795" s="7"/>
     </row>
-    <row r="796">
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I796" s="7"/>
     </row>
-    <row r="797">
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I797" s="7"/>
     </row>
-    <row r="798">
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I798" s="7"/>
     </row>
-    <row r="799">
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I799" s="7"/>
     </row>
-    <row r="800">
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I800" s="7"/>
     </row>
-    <row r="801">
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I801" s="7"/>
     </row>
-    <row r="802">
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I802" s="7"/>
     </row>
-    <row r="803">
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I803" s="7"/>
     </row>
-    <row r="804">
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I804" s="7"/>
     </row>
-    <row r="805">
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I805" s="7"/>
     </row>
-    <row r="806">
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I806" s="7"/>
     </row>
-    <row r="807">
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I807" s="7"/>
     </row>
-    <row r="808">
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I808" s="7"/>
     </row>
-    <row r="809">
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I809" s="7"/>
     </row>
-    <row r="810">
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I810" s="7"/>
     </row>
-    <row r="811">
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I811" s="7"/>
     </row>
-    <row r="812">
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I812" s="7"/>
     </row>
-    <row r="813">
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I813" s="7"/>
     </row>
-    <row r="814">
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I814" s="7"/>
     </row>
-    <row r="815">
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I815" s="7"/>
     </row>
-    <row r="816">
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I816" s="7"/>
     </row>
-    <row r="817">
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I817" s="7"/>
     </row>
-    <row r="818">
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I818" s="7"/>
     </row>
-    <row r="819">
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I819" s="7"/>
     </row>
-    <row r="820">
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I820" s="7"/>
     </row>
-    <row r="821">
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I821" s="7"/>
     </row>
-    <row r="822">
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I822" s="7"/>
     </row>
-    <row r="823">
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I823" s="7"/>
     </row>
-    <row r="824">
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I824" s="7"/>
     </row>
-    <row r="825">
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I825" s="7"/>
     </row>
-    <row r="826">
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I826" s="7"/>
     </row>
-    <row r="827">
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I827" s="7"/>
     </row>
-    <row r="828">
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I828" s="7"/>
     </row>
-    <row r="829">
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I829" s="7"/>
     </row>
-    <row r="830">
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I830" s="7"/>
     </row>
-    <row r="831">
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I831" s="7"/>
     </row>
-    <row r="832">
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I832" s="7"/>
     </row>
-    <row r="833">
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I833" s="7"/>
     </row>
-    <row r="834">
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I834" s="7"/>
     </row>
-    <row r="835">
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I835" s="7"/>
     </row>
-    <row r="836">
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I836" s="7"/>
     </row>
-    <row r="837">
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I837" s="7"/>
     </row>
-    <row r="838">
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I838" s="7"/>
     </row>
-    <row r="839">
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I839" s="7"/>
     </row>
-    <row r="840">
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I840" s="7"/>
     </row>
-    <row r="841">
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I841" s="7"/>
     </row>
-    <row r="842">
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I842" s="7"/>
     </row>
-    <row r="843">
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I843" s="7"/>
     </row>
-    <row r="844">
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I844" s="7"/>
     </row>
-    <row r="845">
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I845" s="7"/>
     </row>
-    <row r="846">
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I846" s="7"/>
     </row>
-    <row r="847">
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I847" s="7"/>
     </row>
-    <row r="848">
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I848" s="7"/>
     </row>
-    <row r="849">
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I849" s="7"/>
     </row>
-    <row r="850">
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I850" s="7"/>
     </row>
-    <row r="851">
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I851" s="7"/>
     </row>
-    <row r="852">
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I852" s="7"/>
     </row>
-    <row r="853">
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I853" s="7"/>
     </row>
-    <row r="854">
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I854" s="7"/>
     </row>
-    <row r="855">
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I855" s="7"/>
     </row>
-    <row r="856">
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I856" s="7"/>
     </row>
-    <row r="857">
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I857" s="7"/>
     </row>
-    <row r="858">
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I858" s="7"/>
     </row>
-    <row r="859">
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I859" s="7"/>
     </row>
-    <row r="860">
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I860" s="7"/>
     </row>
-    <row r="861">
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I861" s="7"/>
     </row>
-    <row r="862">
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I862" s="7"/>
     </row>
-    <row r="863">
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I863" s="7"/>
     </row>
-    <row r="864">
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I864" s="7"/>
     </row>
-    <row r="865">
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I865" s="7"/>
     </row>
-    <row r="866">
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I866" s="7"/>
     </row>
-    <row r="867">
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I867" s="7"/>
     </row>
-    <row r="868">
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I868" s="7"/>
     </row>
-    <row r="869">
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I869" s="7"/>
     </row>
-    <row r="870">
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I870" s="7"/>
     </row>
-    <row r="871">
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I871" s="7"/>
     </row>
-    <row r="872">
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I872" s="7"/>
     </row>
-    <row r="873">
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I873" s="7"/>
     </row>
-    <row r="874">
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I874" s="7"/>
     </row>
-    <row r="875">
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I875" s="7"/>
     </row>
-    <row r="876">
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I876" s="7"/>
     </row>
-    <row r="877">
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I877" s="7"/>
     </row>
-    <row r="878">
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I878" s="7"/>
     </row>
-    <row r="879">
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I879" s="7"/>
     </row>
-    <row r="880">
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I880" s="7"/>
     </row>
-    <row r="881">
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I881" s="7"/>
     </row>
-    <row r="882">
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I882" s="7"/>
     </row>
-    <row r="883">
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I883" s="7"/>
     </row>
-    <row r="884">
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I884" s="7"/>
     </row>
-    <row r="885">
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I885" s="7"/>
     </row>
-    <row r="886">
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I886" s="7"/>
     </row>
-    <row r="887">
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I887" s="7"/>
     </row>
-    <row r="888">
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I888" s="7"/>
     </row>
-    <row r="889">
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I889" s="7"/>
     </row>
-    <row r="890">
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I890" s="7"/>
     </row>
-    <row r="891">
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I891" s="7"/>
     </row>
-    <row r="892">
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I892" s="7"/>
     </row>
-    <row r="893">
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I893" s="7"/>
     </row>
-    <row r="894">
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I894" s="7"/>
     </row>
-    <row r="895">
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I895" s="7"/>
     </row>
-    <row r="896">
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I896" s="7"/>
     </row>
-    <row r="897">
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I897" s="7"/>
     </row>
-    <row r="898">
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I898" s="7"/>
     </row>
-    <row r="899">
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I899" s="7"/>
     </row>
-    <row r="900">
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I900" s="7"/>
     </row>
-    <row r="901">
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I901" s="7"/>
     </row>
-    <row r="902">
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I902" s="7"/>
     </row>
-    <row r="903">
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I903" s="7"/>
     </row>
-    <row r="904">
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I904" s="7"/>
     </row>
-    <row r="905">
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I905" s="7"/>
     </row>
-    <row r="906">
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I906" s="7"/>
     </row>
-    <row r="907">
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I907" s="7"/>
     </row>
-    <row r="908">
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I908" s="7"/>
     </row>
-    <row r="909">
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I909" s="7"/>
     </row>
-    <row r="910">
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I910" s="7"/>
     </row>
-    <row r="911">
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I911" s="7"/>
     </row>
-    <row r="912">
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I912" s="7"/>
     </row>
-    <row r="913">
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I913" s="7"/>
     </row>
-    <row r="914">
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I914" s="7"/>
     </row>
-    <row r="915">
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I915" s="7"/>
     </row>
-    <row r="916">
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I916" s="7"/>
     </row>
-    <row r="917">
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I917" s="7"/>
     </row>
-    <row r="918">
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I918" s="7"/>
     </row>
-    <row r="919">
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I919" s="7"/>
     </row>
-    <row r="920">
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I920" s="7"/>
     </row>
-    <row r="921">
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I921" s="7"/>
     </row>
-    <row r="922">
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I922" s="7"/>
     </row>
-    <row r="923">
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I923" s="7"/>
     </row>
-    <row r="924">
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I924" s="7"/>
     </row>
-    <row r="925">
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I925" s="7"/>
     </row>
-    <row r="926">
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I926" s="7"/>
     </row>
-    <row r="927">
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I927" s="7"/>
     </row>
-    <row r="928">
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I928" s="7"/>
     </row>
-    <row r="929">
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I929" s="7"/>
     </row>
-    <row r="930">
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I930" s="7"/>
     </row>
-    <row r="931">
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I931" s="7"/>
     </row>
-    <row r="932">
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I932" s="7"/>
     </row>
-    <row r="933">
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I933" s="7"/>
     </row>
-    <row r="934">
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I934" s="7"/>
     </row>
-    <row r="935">
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I935" s="7"/>
     </row>
-    <row r="936">
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I936" s="7"/>
     </row>
-    <row r="937">
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I937" s="7"/>
     </row>
-    <row r="938">
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I938" s="7"/>
     </row>
-    <row r="939">
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I939" s="7"/>
     </row>
-    <row r="940">
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I940" s="7"/>
     </row>
-    <row r="941">
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I941" s="7"/>
     </row>
-    <row r="942">
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I942" s="7"/>
     </row>
-    <row r="943">
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I943" s="7"/>
     </row>
-    <row r="944">
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I944" s="7"/>
     </row>
-    <row r="945">
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I945" s="7"/>
     </row>
-    <row r="946">
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I946" s="7"/>
     </row>
-    <row r="947">
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I947" s="7"/>
     </row>
-    <row r="948">
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I948" s="7"/>
     </row>
-    <row r="949">
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I949" s="7"/>
     </row>
-    <row r="950">
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I950" s="7"/>
     </row>
-    <row r="951">
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I951" s="7"/>
     </row>
-    <row r="952">
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I952" s="7"/>
     </row>
-    <row r="953">
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I953" s="7"/>
     </row>
-    <row r="954">
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I954" s="7"/>
     </row>
-    <row r="955">
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I955" s="7"/>
     </row>
-    <row r="956">
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I956" s="7"/>
     </row>
-    <row r="957">
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I957" s="7"/>
     </row>
-    <row r="958">
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I958" s="7"/>
     </row>
-    <row r="959">
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I959" s="7"/>
     </row>
-    <row r="960">
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I960" s="7"/>
     </row>
-    <row r="961">
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I961" s="7"/>
     </row>
-    <row r="962">
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I962" s="7"/>
     </row>
-    <row r="963">
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I963" s="7"/>
     </row>
-    <row r="964">
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I964" s="7"/>
     </row>
-    <row r="965">
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I965" s="7"/>
     </row>
-    <row r="966">
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I966" s="7"/>
     </row>
-    <row r="967">
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I967" s="7"/>
     </row>
-    <row r="968">
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I968" s="7"/>
     </row>
-    <row r="969">
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I969" s="7"/>
     </row>
-    <row r="970">
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I970" s="7"/>
     </row>
-    <row r="971">
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I971" s="7"/>
     </row>
-    <row r="972">
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I972" s="7"/>
     </row>
-    <row r="973">
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I973" s="7"/>
     </row>
-    <row r="974">
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I974" s="7"/>
     </row>
-    <row r="975">
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I975" s="7"/>
     </row>
-    <row r="976">
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I976" s="7"/>
     </row>
-    <row r="977">
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I977" s="7"/>
     </row>
-    <row r="978">
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I978" s="7"/>
     </row>
-    <row r="979">
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I979" s="7"/>
     </row>
-    <row r="980">
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I980" s="7"/>
     </row>
-    <row r="981">
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I981" s="7"/>
     </row>
-    <row r="982">
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I982" s="7"/>
     </row>
-    <row r="983">
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I983" s="7"/>
     </row>
-    <row r="984">
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I984" s="7"/>
     </row>
-    <row r="985">
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I985" s="7"/>
     </row>
-    <row r="986">
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I986" s="7"/>
     </row>
-    <row r="987">
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I987" s="7"/>
     </row>
-    <row r="988">
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I988" s="7"/>
     </row>
-    <row r="989">
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I989" s="7"/>
     </row>
-    <row r="990">
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I990" s="7"/>
     </row>
-    <row r="991">
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I991" s="7"/>
     </row>
-    <row r="992">
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I992" s="7"/>
     </row>
-    <row r="993">
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I993" s="7"/>
     </row>
-    <row r="994">
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I994" s="7"/>
     </row>
-    <row r="995">
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I995" s="7"/>
     </row>
-    <row r="996">
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I996" s="7"/>
     </row>
-    <row r="997">
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I997" s="7"/>
     </row>
-    <row r="998">
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I998" s="7"/>
     </row>
-    <row r="999">
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I999" s="7"/>
     </row>
-    <row r="1000">
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I1000" s="7"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>